--- a/results/final_0624_summary/VirusPseAAC_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/VirusPseAAC_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.3758±0.0454</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.3264±0.0484</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.2730±0.0315</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.2440±0.0266</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.7731±0.0703</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.8060±0.0629</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.8482±0.0370</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.8725±0.0567</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.4634±0.0404</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.4247±0.0494</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.3874±0.0273</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.3685±0.0330</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.5782±0.0251</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5038±0.0587</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.4376±0.0498</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.3874±0.0529</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.3593±0.0429</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.3116±0.0448</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.2654±0.0300</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.2418±0.0271</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.3516±0.0360</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.3240±0.0241</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.3238±0.0181</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.3132±0.0221</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.2550±0.0221</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.2283±0.0192</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.2226±0.0124</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.2134±0.0162</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6697±0.0985</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6840±0.0839</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.7500±0.0927</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.7683±0.0885</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.7736±0.0406</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.8278±0.0966</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.8772±0.0796</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.9263±0.0592</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.4256±0.0242</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.3970±0.0467</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.3818±0.0232</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.3678±0.0295</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.2942±0.0165</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.2647±0.0370</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.2465±0.0198</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.2330±0.0206</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.7719±0.0636</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.7998±0.0623</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.8538±0.0379</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.8762±0.0575</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.1308±0.0571</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.0750±0.0415</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.0265±0.0292</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0073±0.0111</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.3730±0.0471</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.3230±0.0496</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.2724±0.0301</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.2438±0.0265</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7803±0.0774</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.8072±0.0658</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.8506±0.0365</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.8749±0.0565</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.4646±0.0464</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.4228±0.0515</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.3875±0.0261</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.3686±0.0331</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.5773±0.0275</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.5030±0.0588</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.4368±0.0499</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.3870±0.0531</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.3590±0.0480</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.3083±0.0465</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.2648±0.0284</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.2415±0.0270</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.3532±0.0393</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.3240±0.0256</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.3245±0.0186</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.3138±0.0220</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.2560±0.0249</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.2281±0.0203</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.2229±0.0123</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.2135±0.0162</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6743±0.1036</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6848±0.0852</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7583±0.0979</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7711±0.0868</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.8126±0.0405</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.8363±0.0929</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.8807±0.0727</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.9299±0.0603</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.4277±0.0281</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.3971±0.0478</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.3821±0.0230</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.3682±0.0297</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.2950±0.0188</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.2645±0.0374</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.2465±0.0197</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.2332±0.0207</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7803±0.0719</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.8017±0.0667</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.8559±0.0373</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.8784±0.0577</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.1259±0.0606</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.0678±0.0390</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.0242±0.0240</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0073±0.0111</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.3733±0.0490</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.3276±0.0508</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.2730±0.0315</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.2440±0.0266</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.7682±0.0777</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.8060±0.0629</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.8482±0.0370</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.8725±0.0567</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.4601±0.0456</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.4255±0.0509</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.3874±0.0273</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.3685±0.0330</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.5774±0.0259</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.5042±0.0595</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.4376±0.0498</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.3874±0.0529</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.3568±0.0460</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.3128±0.0474</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.2654±0.0300</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.2418±0.0271</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.3509±0.0366</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.3242±0.0242</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.3238±0.0181</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.3132±0.0221</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.2548±0.0224</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.2286±0.0194</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.2226±0.0124</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.2134±0.0162</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.6677±0.0991</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.6840±0.0839</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.7500±0.0927</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.7683±0.0885</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.7531±0.0305</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.8278±0.0966</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.8772±0.0796</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.9263±0.0592</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.4238±0.0275</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.3972±0.0472</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.3818±0.0232</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.3678±0.0295</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.2930±0.0184</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.2650±0.0376</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.2465±0.0198</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.2330±0.0206</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.7680±0.0702</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.7998±0.0623</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.8538±0.0379</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.8762±0.0575</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.1308±0.0571</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.0775±0.0461</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.0265±0.0292</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0073±0.0111</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.3730±0.0471</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.3230±0.0496</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.2724±0.0301</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.2430±0.0264</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.7803±0.0774</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.8072±0.0658</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.8506±0.0365</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.8725±0.0567</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.4646±0.0464</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.4228±0.0515</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.3875±0.0261</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.3674±0.0327</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.5773±0.0275</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.5030±0.0588</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.4368±0.0499</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.3858±0.0515</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.3590±0.0480</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.3083±0.0465</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.2648±0.0284</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.2407±0.0268</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.3532±0.0393</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.3240±0.0256</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.3245±0.0186</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.3125±0.0223</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.2560±0.0249</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.2281±0.0203</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.2229±0.0123</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.2127±0.0166</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.6743±0.1036</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.6848±0.0852</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.7583±0.0979</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.7683±0.0885</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.8126±0.0405</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.8363±0.0929</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.8807±0.0727</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.9299±0.0603</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.4277±0.0281</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.3971±0.0478</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.3821±0.0230</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.3672±0.0294</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.2950±0.0188</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.2645±0.0374</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.2465±0.0197</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.2324±0.0205</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.7803±0.0719</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.8017±0.0667</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.8559±0.0373</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.8762±0.0575</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.1259±0.0606</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.0678±0.0390</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.0242±0.0240</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0073±0.0111</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.4012±0.0526</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.3826±0.0743</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.3550±0.0591</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.3213±0.0425</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.6804±0.0413</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.6703±0.0733</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.6833±0.0701</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.6835±0.0858</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.4554±0.0464</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.4393±0.0676</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.4303±0.0522</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.4097±0.0418</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.6008±0.0364</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.5855±0.0625</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.6010±0.0706</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.5938±0.0689</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.3749±0.0453</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.3527±0.0650</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.3307±0.0522</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.3053±0.0391</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.3379±0.0437</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.3122±0.0325</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.3306±0.0364</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.3183±0.0393</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.2577±0.0285</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.2391±0.0289</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.2536±0.0328</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.2394±0.0243</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5981±0.1136</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.5597±0.1013</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.5786±0.0993</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.5708±0.1340</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.6059±0.0890</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.6607±0.1194</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.6843±0.1016</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.7626±0.1245</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.4094±0.0284</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.3942±0.0577</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.4124±0.0514</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.4080±0.0444</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.2931±0.0233</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.2832±0.0516</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.2979±0.0474</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.2930±0.0378</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.6802±0.0390</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.6580±0.0770</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.6818±0.0652</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.6852±0.0884</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.2033±0.0460</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.1644±0.0629</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.1015±0.0572</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.0630±0.0616</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.3876±0.0449</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.3716±0.0698</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.3343±0.0463</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.3134±0.0393</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.7100±0.0557</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.7132±0.0704</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.7281±0.0651</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.7445±0.0566</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.4555±0.0427</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.4458±0.0646</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.4299±0.0450</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.4192±0.0388</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.6007±0.0324</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.5839±0.0598</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.5868±0.0617</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.5774±0.0653</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.3617±0.0403</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.3507±0.0611</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.3184±0.0430</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.3010±0.0383</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.3397±0.0515</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.3228±0.0346</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.3299±0.0300</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.3256±0.0306</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.2572±0.0365</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.2427±0.0276</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.2462±0.0252</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.2362±0.0189</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.6057±0.1197</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.5877±0.1021</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.5989±0.0890</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.6180±0.1190</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.6466±0.0606</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.7112±0.0964</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.7604±0.1022</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.8230±0.1307</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.4173±0.0302</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.4101±0.0554</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.4189±0.0457</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.4188±0.0380</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.2967±0.0219</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.2902±0.0475</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.2954±0.0399</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.2928±0.0336</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.7046±0.0578</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.7074±0.0779</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.7276±0.0591</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.7438±0.0591</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.1499±0.0425</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.1353±0.0594</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.0628±0.0447</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.0340±0.0348</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.4039±0.0533</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.3792±0.0800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.3541±0.0522</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.3224±0.0459</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6707±0.0399</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6498±0.0724</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6736±0.0659</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.6715±0.0846</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.4520±0.0472</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.4311±0.0728</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.4256±0.0473</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.4073±0.0419</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.6000±0.0368</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.5815±0.0653</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.5990±0.0671</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.5935±0.0717</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.3724±0.0502</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.3488±0.0713</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.3274±0.0461</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.3063±0.0421</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.3363±0.0438</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.3071±0.0330</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.3264±0.0332</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.3133±0.0336</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.2582±0.0285</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.2359±0.0275</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.2506±0.0301</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.2367±0.0205</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5925±0.1137</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.5509±0.1031</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.5714±0.0963</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.5632±0.1302</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.5836±0.0916</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.6476±0.1276</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.6842±0.0903</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.7523±0.1360</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.4047±0.0287</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.3858±0.0595</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.4073±0.0500</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.4037±0.0442</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.2905±0.0236</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.2779±0.0537</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.2943±0.0461</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.2913±0.0393</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.6685±0.0407</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.6403±0.0750</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.6717±0.0627</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.6730±0.0883</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.2033±0.0630</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.1740±0.0698</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.1015±0.0481</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.0727±0.0653</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.3846±0.0470</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.3704±0.0697</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.3362±0.0458</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.3131±0.0403</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.7196±0.0497</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.7108±0.0723</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.7313±0.0693</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.7421±0.0537</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.4563±0.0415</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.4443±0.0646</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.4320±0.0441</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.4180±0.0381</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.6015±0.0316</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.5823±0.0587</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.5885±0.0602</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.5766±0.0650</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.3602±0.0416</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.3496±0.0609</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.3205±0.0424</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.3002±0.0386</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.3408±0.0526</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.3210±0.0337</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.3317±0.0296</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.3239±0.0259</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.2578±0.0376</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.2413±0.0270</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.2474±0.0246</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.2350±0.0162</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.6094±0.1184</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.5843±0.1016</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.6030±0.0894</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.6143±0.1146</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.6561±0.0515</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.7087±0.0896</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.7623±0.0990</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.8256±0.1294</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.4204±0.0270</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.4083±0.0551</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.4209±0.0447</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.4176±0.0381</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.2984±0.0193</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.2888±0.0470</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.2968±0.0391</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.2921±0.0342</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.7123±0.0523</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.7053±0.0797</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.7312±0.0602</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.7417±0.0570</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.1452±0.0468</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.1353±0.0594</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.0628±0.0486</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.0340±0.0348</t>
         </is>
@@ -1419,80 +3039,260 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.3216±0.0598</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.3313±0.0781</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.3003±0.0515</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.2778±0.0741</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.2927±0.0673</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.3159±0.0605</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.2979±0.0484</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.3190±0.0890</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.2999±0.0619</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.3119±0.0659</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.2877±0.0412</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.2790±0.0753</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.8221±0.0193</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.8096±0.0265</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.8024±0.0181</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.7549±0.0322</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.2854±0.0601</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.2894±0.0632</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.2651±0.0345</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.2430±0.0675</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.2495±0.0935</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.2545±0.0721</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.2765±0.1148</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.2410±0.0959</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.3096±0.0656</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.2956±0.0569</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.3640±0.1575</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.2947±0.1424</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.2208±0.1007</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.2357±0.0804</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.2514±0.1111</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.2523±0.1041</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>0.9857±0.0429</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>0.9639±0.0337</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.3832±0.0752</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.3940±0.0808</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.3701±0.0577</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.3370±0.0902</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.6438±0.0884</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.5584±0.1191</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.5301±0.0899</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.3742±0.0868</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.2761±0.0690</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.3059±0.0655</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.2880±0.0530</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.3122±0.0950</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.2419±0.0563</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.2225±0.0610</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.1981±0.0260</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.1423±0.0595</t>
         </is>
@@ -1526,80 +3326,260 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0.3075±0.0760</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.3117±0.0620</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.3197±0.0917</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.2445±0.0582</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.2808±0.0755</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.2946±0.0608</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.3098±0.0889</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.2898±0.0691</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>0.2857±0.0727</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.2931±0.0577</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.3026±0.0824</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.2493±0.0585</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.8181±0.0164</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.8104±0.0177</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.8076±0.0211</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.7454±0.0358</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.2688±0.0685</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.2733±0.0539</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.2785±0.0721</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.2176±0.0533</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.2414±0.0996</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.2357±0.0816</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.2609±0.0821</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.2188±0.0507</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.2954±0.0837</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.2836±0.0674</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.3577±0.1038</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.2736±0.0608</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.2149±0.1033</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.2147±0.0909</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.2346±0.0847</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.2398±0.0830</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>0.9949±0.0101</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.9349±0.0504</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.3659±0.0783</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.3768±0.0658</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.3829±0.0841</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.3121±0.0601</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.6169±0.0555</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.5656±0.0822</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.5597±0.1229</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.3551±0.0666</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.2636±0.0702</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.2854±0.0607</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.3020±0.0891</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.2879±0.0777</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.2179±0.0567</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.2152±0.0461</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.2075±0.0582</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.1329±0.0465</t>
         </is>
@@ -1633,82 +3613,1123 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0.0098±0.0119</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.0303±0.0249</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0615±0.0622</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0889±0.0515</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.0073±0.0098</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0278±0.0259</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0579±0.0570</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0869±0.0510</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>0.0081±0.0103</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>0.0282±0.0255</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.0587±0.0581</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0.0845±0.0478</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0.7987±0.0117</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.8003±0.0122</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.8039±0.0172</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.8003±0.0089</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.0073±0.0098</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.0266±0.0263</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.0567±0.0551</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.0792±0.0437</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.0087±0.0107</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.0605±0.0645</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.0771±0.0683</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.1049±0.0686</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.0667±0.0816</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.1500±0.1106</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.1507±0.1007</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.1895±0.0517</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.0046±0.0057</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.0462±0.0556</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0613±0.0602</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.0828±0.0678</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.0159±0.0194</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.0494±0.0383</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.0937±0.0915</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.1348±0.0763</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.4000±0.4899</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0.6250±0.3750</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.6772±0.3678</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.6118±0.2119</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.0081±0.0099</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.0260±0.0206</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.0536±0.0560</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.0803±0.0497</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
         <is>
           <t>0.0049±0.0098</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.0218±0.0295</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.0507±0.0464</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.0651±0.0357</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.6760±0.0149</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.6823±0.0334</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.6193±0.0888</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.6245±0.0957</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.3074±0.0831</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.2792±0.0746</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.3078±0.0867</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.2795±0.1084</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.2808±0.0815</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.2598±0.0756</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.3126±0.0979</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.2992±0.1191</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.2872±0.0817</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.2611±0.0725</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.2956±0.0854</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.2717±0.1034</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.8230±0.0269</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.8205±0.0205</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.7955±0.0203</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.7730±0.0258</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.2735±0.0814</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.2441±0.0703</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.2693±0.0780</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.2379±0.0873</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.2395±0.0940</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.2324±0.0946</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.2349±0.1059</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.2221±0.0893</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.3067±0.0916</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.3035±0.0905</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.2760±0.1139</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.2731±0.1083</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.2128±0.0986</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.2065±0.0953</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.2237±0.1156</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.2098±0.0993</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>0.9949±0.0154</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0.9766±0.0276</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.3715±0.0969</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.3554±0.0829</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.3724±0.0886</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.3348±0.0995</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.6592±0.1508</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.6554±0.0936</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.4930±0.0770</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.4095±0.0864</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.2598±0.0736</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.2483±0.0709</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.3094±0.0970</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.2927±0.1157</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.2324±0.0851</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.1934±0.0665</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.1934±0.0585</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.1423±0.0596</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.5400±0.0398</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.5456±0.0590</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.4674±0.0916</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.4162±0.0905</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.5609±0.0658</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.4986±0.0430</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.3923±0.0807</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.2540±0.0639</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.4858±0.0536</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.4656±0.0604</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.4213±0.0720</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.3659±0.0851</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.5100±0.0565</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.4631±0.0427</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.3829±0.0712</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.2754±0.0619</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.8165±0.0214</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.7951±0.0188</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.7653±0.0351</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.6815±0.0246</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.4858±0.0536</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.4276±0.0400</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.3352±0.0729</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.2204±0.0523</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.3158±0.0878</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.3096±0.0801</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.3039±0.0850</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.2418±0.0330</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.3304±0.0956</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.3354±0.0857</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.3016±0.0872</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.2260±0.0228</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.3230±0.0967</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.3261±0.0922</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.3368±0.0925</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.3278±0.0891</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.9670±0.0553</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.8323±0.0819</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.5046±0.0554</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.4710±0.0435</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.4189±0.0714</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.3067±0.0536</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.5577±0.0613</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.4950±0.0396</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.4275±0.0876</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.2748±0.0420</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.4613±0.0532</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.4515±0.0595</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.4168±0.0735</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.3511±0.0796</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.4157±0.0486</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.3236±0.0517</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.2003±0.0897</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0843±0.0494</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.5789±0.0627</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.5837±0.0677</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.5601±0.1146</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.5156±0.1244</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.4394±0.0703</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.3574±0.0626</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.3590±0.0852</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.3389±0.0975</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.4523±0.0769</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.3718±0.0644</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.4085±0.1137</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.4579±0.1664</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.4288±0.0671</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.3500±0.0589</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.3616±0.0875</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.3653±0.1132</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.8115±0.0269</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.7923±0.0298</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.7842±0.0280</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.7220±0.0505</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.3943±0.0554</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.3207±0.0574</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.3176±0.0707</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.3093±0.0976</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.2783±0.0770</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.2606±0.0877</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.2699±0.0886</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.2546±0.0969</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.2852±0.0913</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.3183±0.1033</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.3018±0.1153</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.2443±0.0785</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.2937±0.0853</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.2600±0.1027</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.2812±0.1056</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.3303±0.1895</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.9916±0.0179</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.9134±0.1609</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.4876±0.0704</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.4068±0.0653</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.4227±0.0695</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.3852±0.1063</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.5447±0.0738</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.4917±0.0797</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.4738±0.0628</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.3510±0.0834</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.4444±0.0782</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.3527±0.0715</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.3988±0.1019</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.4458±0.1647</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.2895±0.0463</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.2344±0.0636</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.1934±0.0415</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1642±0.0727</t>
         </is>
       </c>
     </row>
